--- a/Mechanical/Connectors/Debug/Database/Mechanical_Connectors_Debug_GOST.xlsx
+++ b/Mechanical/Connectors/Debug/Database/Mechanical_Connectors_Debug_GOST.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr showInkAnnotation="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,22 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Electronics\Mechanical\Connectors\Debug\Database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{14DAEB5E-6EA2-49DA-8749-33B45E5C8ADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A68E2A4A-6D61-4E55-9027-A77C0CD3EFB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11235"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="List" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="144525"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -184,9 +177,6 @@
     <t>Debug</t>
   </si>
   <si>
-    <t>..\Footprints\Mechanical_Connectors_Debug_TH.PcbLib</t>
-  </si>
-  <si>
     <t>SWD</t>
   </si>
   <si>
@@ -254,12 +244,15 @@
   </si>
   <si>
     <t>13.2mm</t>
+  </si>
+  <si>
+    <t>..\Footprints\Mechanical_Connectors_Debug_THT.PcbLib</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -579,7 +572,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AM4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -737,55 +730,55 @@
     </row>
     <row r="2" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="D2" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>67</v>
-      </c>
       <c r="F2" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>47</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>37</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>41</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P2" s="1" t="s">
         <v>42</v>
       </c>
       <c r="Q2" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="X2" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="X2" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="Y2" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AA2" s="1" t="s">
         <v>45</v>
@@ -793,16 +786,16 @@
       <c r="AD2" s="2"/>
       <c r="AE2" s="2"/>
       <c r="AF2" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AG2" s="1" t="s">
         <v>48</v>
       </c>
       <c r="AH2" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="AJ2" s="1" t="s">
         <v>43</v>
@@ -816,19 +809,19 @@
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>47</v>
@@ -840,31 +833,31 @@
         <v>37</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>41</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P3" s="1" t="s">
         <v>42</v>
       </c>
       <c r="Q3" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="X3" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="X3" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="Y3" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AA3" s="1" t="s">
         <v>45</v>
@@ -872,16 +865,16 @@
       <c r="AD3" s="2"/>
       <c r="AE3" s="2"/>
       <c r="AF3" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AG3" s="1" t="s">
         <v>48</v>
       </c>
       <c r="AH3" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AI3" s="1" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="AJ3" s="1" t="s">
         <v>43</v>
@@ -895,19 +888,19 @@
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>47</v>
@@ -919,31 +912,31 @@
         <v>37</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>41</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P4" s="1" t="s">
         <v>42</v>
       </c>
       <c r="Q4" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="X4" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="X4" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="Y4" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Z4" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AA4" s="1" t="s">
         <v>45</v>
@@ -951,16 +944,16 @@
       <c r="AD4" s="2"/>
       <c r="AE4" s="2"/>
       <c r="AF4" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AG4" s="1" t="s">
         <v>48</v>
       </c>
       <c r="AH4" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AI4" s="1" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="AJ4" s="1" t="s">
         <v>43</v>

--- a/Mechanical/Connectors/Debug/Database/Mechanical_Connectors_Debug_GOST.xlsx
+++ b/Mechanical/Connectors/Debug/Database/Mechanical_Connectors_Debug_GOST.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Electronics\Mechanical\Connectors\Debug\Database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A68E2A4A-6D61-4E55-9027-A77C0CD3EFB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BF0937A-CF96-4E9D-8EA4-9451BDF5F2DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2685" yWindow="2685" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="List" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="76">
   <si>
     <t>Item ID</t>
   </si>
@@ -247,6 +247,12 @@
   </si>
   <si>
     <t>..\Footprints\Mechanical_Connectors_Debug_THT.PcbLib</t>
+  </si>
+  <si>
+    <t>Shielding</t>
+  </si>
+  <si>
+    <t>Unshielded</t>
   </si>
 </sst>
 </file>
@@ -573,7 +579,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AM4"/>
+  <dimension ref="A1:AN4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -589,27 +595,27 @@
     <col min="12" max="14" width="7.140625" style="1" customWidth="1"/>
     <col min="15" max="15" width="13" style="1" customWidth="1"/>
     <col min="16" max="16" width="7.140625" style="1" customWidth="1"/>
-    <col min="17" max="17" width="6.7109375" style="1" customWidth="1"/>
-    <col min="18" max="18" width="7" style="1" customWidth="1"/>
-    <col min="19" max="19" width="4.5703125" style="1" customWidth="1"/>
-    <col min="20" max="21" width="4" style="1" customWidth="1"/>
-    <col min="22" max="23" width="4.5703125" style="1" customWidth="1"/>
-    <col min="24" max="26" width="7" style="1" customWidth="1"/>
-    <col min="27" max="27" width="11.7109375" style="1" customWidth="1"/>
-    <col min="28" max="28" width="5" style="1" customWidth="1"/>
-    <col min="29" max="31" width="7.85546875" style="1" customWidth="1"/>
-    <col min="32" max="32" width="10.7109375" style="1" customWidth="1"/>
-    <col min="33" max="33" width="5.7109375" style="1" customWidth="1"/>
-    <col min="34" max="34" width="13" style="1" customWidth="1"/>
-    <col min="35" max="35" width="5.85546875" style="1" customWidth="1"/>
-    <col min="36" max="36" width="8.85546875" style="1" customWidth="1"/>
-    <col min="37" max="37" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="16384" width="9.140625" style="1"/>
+    <col min="17" max="18" width="6.7109375" style="1" customWidth="1"/>
+    <col min="19" max="19" width="7" style="1" customWidth="1"/>
+    <col min="20" max="20" width="4.5703125" style="1" customWidth="1"/>
+    <col min="21" max="22" width="4" style="1" customWidth="1"/>
+    <col min="23" max="24" width="4.5703125" style="1" customWidth="1"/>
+    <col min="25" max="27" width="7" style="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="1" customWidth="1"/>
+    <col min="29" max="29" width="5" style="1" customWidth="1"/>
+    <col min="30" max="32" width="7.85546875" style="1" customWidth="1"/>
+    <col min="33" max="33" width="10.7109375" style="1" customWidth="1"/>
+    <col min="34" max="34" width="5.7109375" style="1" customWidth="1"/>
+    <col min="35" max="35" width="13" style="1" customWidth="1"/>
+    <col min="36" max="36" width="5.85546875" style="1" customWidth="1"/>
+    <col min="37" max="37" width="8.85546875" style="1" customWidth="1"/>
+    <col min="38" max="38" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -662,73 +668,76 @@
         <v>35</v>
       </c>
       <c r="R1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>64</v>
       </c>
@@ -771,43 +780,46 @@
       <c r="Q2" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="X2" s="1" t="s">
+      <c r="R2" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y2" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="Z2" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="Z2" s="1" t="s">
+      <c r="AA2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="AA2" s="1" t="s">
+      <c r="AB2" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AD2" s="2"/>
       <c r="AE2" s="2"/>
-      <c r="AF2" s="1" t="s">
+      <c r="AF2" s="2"/>
+      <c r="AG2" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="AG2" s="1" t="s">
+      <c r="AH2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AH2" s="1" t="s">
+      <c r="AI2" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="AI2" s="1" t="s">
+      <c r="AJ2" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="AJ2" s="1" t="s">
+      <c r="AK2" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AK2" s="1" t="s">
+      <c r="AL2" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AL2" s="1" t="s">
+      <c r="AM2" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>53</v>
       </c>
@@ -850,43 +862,46 @@
       <c r="Q3" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="X3" s="1" t="s">
+      <c r="R3" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y3" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="Y3" s="1" t="s">
+      <c r="Z3" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="Z3" s="1" t="s">
+      <c r="AA3" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="AA3" s="1" t="s">
+      <c r="AB3" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AD3" s="2"/>
       <c r="AE3" s="2"/>
-      <c r="AF3" s="1" t="s">
+      <c r="AF3" s="2"/>
+      <c r="AG3" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AG3" s="1" t="s">
+      <c r="AH3" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AH3" s="1" t="s">
+      <c r="AI3" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="AI3" s="1" t="s">
+      <c r="AJ3" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="AJ3" s="1" t="s">
+      <c r="AK3" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AK3" s="1" t="s">
+      <c r="AL3" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AL3" s="1" t="s">
+      <c r="AM3" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>60</v>
       </c>
@@ -929,39 +944,42 @@
       <c r="Q4" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="X4" s="1" t="s">
+      <c r="R4" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y4" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="Y4" s="1" t="s">
+      <c r="Z4" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="Z4" s="1" t="s">
+      <c r="AA4" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="AA4" s="1" t="s">
+      <c r="AB4" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AD4" s="2"/>
       <c r="AE4" s="2"/>
-      <c r="AF4" s="1" t="s">
+      <c r="AF4" s="2"/>
+      <c r="AG4" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="AG4" s="1" t="s">
+      <c r="AH4" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AH4" s="1" t="s">
+      <c r="AI4" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="AI4" s="1" t="s">
+      <c r="AJ4" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="AJ4" s="1" t="s">
+      <c r="AK4" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AK4" s="1" t="s">
+      <c r="AL4" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AL4" s="1" t="s">
+      <c r="AM4" s="1" t="s">
         <v>49</v>
       </c>
     </row>

--- a/Mechanical/Connectors/Debug/Database/Mechanical_Connectors_Debug_GOST.xlsx
+++ b/Mechanical/Connectors/Debug/Database/Mechanical_Connectors_Debug_GOST.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Electronics\Mechanical\Connectors\Debug\Database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BF0937A-CF96-4E9D-8EA4-9451BDF5F2DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{862214F7-B161-4FD8-B73C-FC0B3A8500FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="2685" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2595" yWindow="2595" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="List" sheetId="2" r:id="rId1"/>
@@ -192,9 +192,6 @@
     <t>PCB-PAD-2.54-4</t>
   </si>
   <si>
-    <t>2.54</t>
-  </si>
-  <si>
     <t>PCB-PAD-2.54-5</t>
   </si>
   <si>
@@ -253,6 +250,9 @@
   </si>
   <si>
     <t>Unshielded</t>
+  </si>
+  <si>
+    <t>2.54mm</t>
   </si>
 </sst>
 </file>
@@ -587,7 +587,7 @@
     <col min="3" max="3" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.28515625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.42578125" style="1" customWidth="1"/>
     <col min="7" max="7" width="5.7109375" style="1" customWidth="1"/>
     <col min="8" max="9" width="3" style="1" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" style="1" customWidth="1"/>
@@ -668,7 +668,7 @@
         <v>35</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>34</v>
@@ -739,55 +739,55 @@
     </row>
     <row r="2" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="D2" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="F2" s="1" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>47</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>37</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>41</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="P2" s="1" t="s">
         <v>42</v>
       </c>
       <c r="Q2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y2" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="R2" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="Y2" s="1" t="s">
-        <v>59</v>
-      </c>
       <c r="Z2" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AA2" s="1" t="s">
         <v>51</v>
@@ -798,16 +798,16 @@
       <c r="AE2" s="2"/>
       <c r="AF2" s="2"/>
       <c r="AG2" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AH2" s="1" t="s">
         <v>48</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AJ2" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AK2" s="1" t="s">
         <v>43</v>
@@ -824,7 +824,7 @@
         <v>53</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>53</v>
@@ -833,7 +833,7 @@
         <v>54</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>47</v>
@@ -845,7 +845,7 @@
         <v>37</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>41</v>
@@ -854,22 +854,22 @@
         <v>50</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="P3" s="1" t="s">
         <v>42</v>
       </c>
       <c r="Q3" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y3" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="R3" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="Y3" s="1" t="s">
-        <v>59</v>
-      </c>
       <c r="Z3" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AA3" s="1" t="s">
         <v>51</v>
@@ -889,7 +889,7 @@
         <v>53</v>
       </c>
       <c r="AJ3" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AK3" s="1" t="s">
         <v>43</v>
@@ -903,19 +903,19 @@
     </row>
     <row r="4" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>47</v>
@@ -927,7 +927,7 @@
         <v>37</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>41</v>
@@ -936,22 +936,22 @@
         <v>50</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="P4" s="1" t="s">
         <v>42</v>
       </c>
       <c r="Q4" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y4" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="R4" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="Y4" s="1" t="s">
-        <v>59</v>
-      </c>
       <c r="Z4" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AA4" s="1" t="s">
         <v>51</v>
@@ -968,10 +968,10 @@
         <v>48</v>
       </c>
       <c r="AI4" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AJ4" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AK4" s="1" t="s">
         <v>43</v>
